--- a/tutorials/Sleep.xlsx
+++ b/tutorials/Sleep.xlsx
@@ -1,28 +1,28 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10811"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10315"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dbw209/Library/Mobile Documents/com~apple~CloudDocs/Documents/Research/systemdynamics/Examples/Kumu/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dbw209/Library/Mobile Documents/com~apple~CloudDocs/Documents/Research/systemdynamics/tutorials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{98F609A5-1130-8443-ADFA-F9CE1B1BCFC6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB274459-EC09-FF44-AA94-14C996E6639C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="760" windowWidth="30240" windowHeight="18880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elements" sheetId="1" r:id="rId1"/>
     <sheet name="Connections" sheetId="2" r:id="rId2"/>
     <sheet name="Interactions" sheetId="3" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="23">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="24">
   <si>
     <t>Label</t>
   </si>
@@ -91,6 +91,9 @@
   </si>
   <si>
     <t>From2</t>
+  </si>
+  <si>
+    <t>VOI</t>
   </si>
 </sst>
 </file>
@@ -499,6 +502,12 @@
       <c r="B2" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C2">
+        <v>-1</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>23</v>
+      </c>
     </row>
     <row r="3" spans="1:4" ht="14" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
@@ -506,6 +515,12 @@
       </c>
       <c r="B3" s="1" t="s">
         <v>19</v>
+      </c>
+      <c r="C3">
+        <v>-1</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14" x14ac:dyDescent="0.15">
@@ -515,6 +530,9 @@
       <c r="B4" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C4">
+        <v>1</v>
+      </c>
     </row>
     <row r="5" spans="1:4" ht="14" x14ac:dyDescent="0.15">
       <c r="A5" t="s">
@@ -523,6 +541,9 @@
       <c r="B5" s="1" t="s">
         <v>20</v>
       </c>
+      <c r="C5">
+        <v>-1</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="14" x14ac:dyDescent="0.15">
       <c r="A6" t="s">
@@ -531,6 +552,9 @@
       <c r="B6" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="C6">
+        <v>-1</v>
+      </c>
     </row>
     <row r="7" spans="1:4" ht="14" x14ac:dyDescent="0.15">
       <c r="A7" t="s">
@@ -539,6 +563,9 @@
       <c r="B7" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="C7">
+        <v>-1</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="14" x14ac:dyDescent="0.15">
       <c r="A8" t="s">
@@ -547,6 +574,9 @@
       <c r="B8" s="1" t="s">
         <v>18</v>
       </c>
+      <c r="C8">
+        <v>1</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="14" x14ac:dyDescent="0.15">
       <c r="A9" t="s">
@@ -554,6 +584,9 @@
       </c>
       <c r="B9" s="1" t="s">
         <v>18</v>
+      </c>
+      <c r="C9">
+        <v>-1</v>
       </c>
     </row>
   </sheetData>
@@ -687,7 +720,7 @@
       <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="E8" t="s">
+      <c r="F8" t="s">
         <v>16</v>
       </c>
     </row>

--- a/tutorials/Sleep.xlsx
+++ b/tutorials/Sleep.xlsx
@@ -8,21 +8,20 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/dbw209/Library/Mobile Documents/com~apple~CloudDocs/Documents/Research/systemdynamics/tutorials/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FB274459-EC09-FF44-AA94-14C996E6639C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF7B79A6-812C-5B40-ABB8-10C7930BFD11}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="15120" yWindow="760" windowWidth="15120" windowHeight="18880" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Elements" sheetId="1" r:id="rId1"/>
     <sheet name="Connections" sheetId="2" r:id="rId2"/>
-    <sheet name="Interactions" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0" iterateDelta="1E-4"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="24">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="104" uniqueCount="22">
   <si>
     <t>Label</t>
   </si>
@@ -85,12 +84,6 @@
   </si>
   <si>
     <t>constant</t>
-  </si>
-  <si>
-    <t>From1</t>
-  </si>
-  <si>
-    <t>From2</t>
   </si>
   <si>
     <t>VOI</t>
@@ -505,9 +498,7 @@
       <c r="C2">
         <v>-1</v>
       </c>
-      <c r="D2" s="1" t="s">
-        <v>23</v>
-      </c>
+      <c r="D2" s="1"/>
     </row>
     <row r="3" spans="1:4" ht="14" x14ac:dyDescent="0.15">
       <c r="A3" t="s">
@@ -520,7 +511,7 @@
         <v>-1</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>23</v>
+        <v>21</v>
       </c>
     </row>
     <row r="4" spans="1:4" ht="14" x14ac:dyDescent="0.15">
@@ -720,7 +711,7 @@
       <c r="C8" t="s">
         <v>15</v>
       </c>
-      <c r="F8" t="s">
+      <c r="E8" t="s">
         <v>16</v>
       </c>
     </row>
@@ -889,44 +880,6 @@
         <v>15</v>
       </c>
       <c r="E20" t="s">
-        <v>16</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1081127A-7B42-0246-A96F-A7185E3DDBD3}">
-  <dimension ref="A1:D2"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
-  <sheetData>
-    <row r="1" spans="1:4" ht="14" x14ac:dyDescent="0.15">
-      <c r="A1" s="1" t="s">
-        <v>21</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>22</v>
-      </c>
-      <c r="C1" s="1" t="s">
-        <v>13</v>
-      </c>
-      <c r="D1" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2" spans="1:4" ht="28" x14ac:dyDescent="0.15">
-      <c r="A2" t="s">
-        <v>4</v>
-      </c>
-      <c r="B2" t="s">
-        <v>9</v>
-      </c>
-      <c r="C2" t="s">
-        <v>5</v>
-      </c>
-      <c r="D2" s="1" t="s">
         <v>16</v>
       </c>
     </row>
